--- a/data/trans_camb/IP19C09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,71</t>
+          <t>-7,09; 1,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,98</t>
+          <t>-5,55; 6,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 6,66</t>
+          <t>-2,38; 6,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,69</t>
+          <t>-3,05; 3,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,91</t>
+          <t>-3,72; 2,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,78</t>
+          <t>-3,33; 3,37</t>
         </is>
       </c>
     </row>
@@ -707,14 +707,14 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 459,68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 542,78</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,31; 216,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,07; 349,97</t>
+          <t>-82,67; 310,21</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,94</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,21</t>
+          <t>0,27; 5,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,09</t>
+          <t>-3,66; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,57</t>
+          <t>-3,65; 3,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,02</t>
+          <t>-1,12; 2,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,89</t>
+          <t>-0,93; 3,46</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 677,52</t>
+          <t>-100,0; 391,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,37; 696,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 547,74</t>
+          <t>-54,96; 495,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 628,78</t>
+          <t>-46,38; 558,27</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,0</t>
+          <t>-4,59; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,8</t>
+          <t>-2,76; 1,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,09</t>
+          <t>-4,76; 1,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,9</t>
+          <t>-5,18; 0,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,44</t>
+          <t>-3,24; 0,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,93</t>
+          <t>-3,04; 0,94</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,97</t>
+          <t>-1,27; 4,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,23</t>
+          <t>-0,7; 5,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -0,14</t>
+          <t>-9,7; -0,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 3,29</t>
+          <t>-7,01; 3,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,04</t>
+          <t>-4,21; 1,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,05</t>
+          <t>-2,87; 2,89</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,12</t>
+          <t>-100,0; 4,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,09; 123,9</t>
+          <t>-78,36; 132,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,11; 75,51</t>
+          <t>-87,84; 84,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 158,86</t>
+          <t>-66,04; 167,89</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,79</t>
+          <t>-1,37; 1,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,06</t>
+          <t>-0,7; 3,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,79</t>
+          <t>-3,02; 0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,56</t>
+          <t>-2,65; 1,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,73</t>
+          <t>-1,74; 0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,51</t>
+          <t>-1,03; 1,64</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 313,53</t>
+          <t>-65,09; 269,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 454,94</t>
+          <t>-38,55; 417,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 40,49</t>
+          <t>-78,16; 31,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 83,44</t>
+          <t>-64,12; 72,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 48,28</t>
+          <t>-60,11; 54,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 94,41</t>
+          <t>-37,04; 103,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,92</t>
+          <t>-7,24; 1,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 6,39</t>
+          <t>-5,3; 6,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,24</t>
+          <t>-2,21; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,07</t>
+          <t>-3,08; 3,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,54</t>
+          <t>-3,87; 2,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 3,37</t>
+          <t>-3,36; 3,12</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 459,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,31; 216,18</t>
+          <t>-86,06; 248,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 310,21</t>
+          <t>-83,91; 266,08</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,99</t>
+          <t>0,61; 6,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,91</t>
+          <t>-3,11; 3,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,08</t>
+          <t>-3,06; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,96</t>
+          <t>-1,27; 2,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,46</t>
+          <t>-0,86; 3,37</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 391,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,03; 520,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 495,97</t>
+          <t>-68,38; 372,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,38; 558,27</t>
+          <t>-47,38; 563,33</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,0</t>
+          <t>-3,73; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,82</t>
+          <t>-2,83; 1,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,59</t>
+          <t>-5,06; 0,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,95</t>
+          <t>-4,78; 0,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,43</t>
+          <t>-3,31; 0,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,94</t>
+          <t>-3,01; 1,01</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,92</t>
+          <t>-0,7; 4,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,58</t>
+          <t>-0,72; 5,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -0,82</t>
+          <t>-9,32; -0,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,62</t>
+          <t>-7,05; 3,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,0</t>
+          <t>-4,37; 0,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,89</t>
+          <t>-2,72; 3,0</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,04</t>
+          <t>-100,0; 45,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 132,66</t>
+          <t>-78,76; 132,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,84; 84,35</t>
+          <t>-89,52; 81,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 167,89</t>
+          <t>-62,15; 174,49</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,94</t>
+          <t>-1,17; 1,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,03</t>
+          <t>-0,45; 2,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,47</t>
+          <t>-3,15; 0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,38</t>
+          <t>-2,65; 1,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,72</t>
+          <t>-1,78; 0,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,64</t>
+          <t>-1,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,09; 269,82</t>
+          <t>-60,85; 267,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 417,3</t>
+          <t>-35,38; 408,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 31,07</t>
+          <t>-75,74; 42,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 72,04</t>
+          <t>-65,43; 69,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 54,03</t>
+          <t>-60,94; 48,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 103,19</t>
+          <t>-36,1; 92,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-2,18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 1,81</t>
+          <t>-2,26; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,73</t>
+          <t>-3,13; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 6,73</t>
+          <t>-7,78; 1,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,28</t>
+          <t>-5,26; 5,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,57</t>
+          <t>-3,35; 2,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,12</t>
+          <t>-3,41; 3,78</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-24,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-54,74%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-0,6%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>68,43%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-24,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 542,78</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-86,06; 248,67</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,91; 266,08</t>
+          <t>-85,07; 349,97</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2,55</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>-3,65; 3,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,34</t>
+          <t>-3,57; 3,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 3,02</t>
+          <t>-0,01; 4,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,71</t>
+          <t>0,2; 6,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,71</t>
+          <t>-0,96; 3,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,37</t>
+          <t>-0,65; 3,89</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-2,99%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>346,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>483,29%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,99%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 677,52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-86,37; 696,51</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-86,03; 520,57</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,38; 372,51</t>
+          <t>-49,7; 547,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 563,33</t>
+          <t>-45,65; 628,78</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,02</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,0</t>
+          <t>-5,17; 1,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,8</t>
+          <t>-5,2; 0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,92</t>
+          <t>-4,6; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,98</t>
+          <t>-2,75; 1,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,41</t>
+          <t>-3,33; 0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,01</t>
+          <t>-2,95; 0,93</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-63,74%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-64,94%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-2,15%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-63,74%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-64,94%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,49</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,62</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,49</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,92</t>
+          <t>-9,96; -0,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,3</t>
+          <t>-7,08; 3,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -0,1</t>
+          <t>-1,04; 5,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 3,46</t>
+          <t>-0,69; 5,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,94</t>
+          <t>-4,29; 1,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,0</t>
+          <t>-2,94; 3,05</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-75,83%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-25,15%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>170,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>231,3%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-75,83%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-25,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 27,12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-80,09; 123,9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 45,97</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-78,76; 132,73</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,52; 81,5</t>
+          <t>-91,11; 75,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,15; 174,49</t>
+          <t>-66,15; 158,86</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,15</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,85</t>
+          <t>-3,14; 0,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,9</t>
+          <t>-2,63; 1,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,66</t>
+          <t>-1,17; 1,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,35</t>
+          <t>-0,49; 3,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,73</t>
+          <t>-1,69; 0,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,5</t>
+          <t>-1,08; 1,51</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-40,5%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-21,11%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>16,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>82,66%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-40,5%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-21,11%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,85; 267,64</t>
+          <t>-76,29; 40,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 408,48</t>
+          <t>-66,26; 83,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 42,4</t>
+          <t>-62,92; 313,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 69,45</t>
+          <t>-37,11; 454,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 48,64</t>
+          <t>-60,39; 48,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 92,91</t>
+          <t>-37,48; 94,41</t>
         </is>
       </c>
     </row>
